--- a/src/assets/csv/New Seniors Content June 2023.xlsx
+++ b/src/assets/csv/New Seniors Content June 2023.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/dev/ministry-seniors-accessibility/src/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E0C48F-3317-9348-BB7A-E509F7921E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A8B2DF-C090-7B4A-B307-468B03A3FC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{95B3A603-6A4D-4342-871D-91926965E3B0}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{95B3A603-6A4D-4342-871D-91926965E3B0}"/>
   </bookViews>
   <sheets>
     <sheet name="English Seniors Content June 20" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="695">
   <si>
     <t>Resource title</t>
   </si>
@@ -2299,46 +2299,6 @@
   - [ConnexOntario](https://www.connexontario.ca/en-ca/) provides 24/7 counselling and referrals for mental health, drug and alcohol addiction and problems with gambling.</t>
   </si>
   <si>
-    <t>Use our map to find programs that promote wellness, social connectedness and learning in your community.
-Clubs and groups
-Find social activities and hobbies in your community through organizations such as: 
-    - [YMCA](https://www.ymca.ca/locations?type=ymca,camps&amp;amenities)
-    - [Club Rotary](https://my.rotary.org/en/club-search)
-    - [Lions Club](https://www.lionsclubs.org/en/start-our-approach/club-locator)
-    - [Royal Canadian Legion](https://legion.ca/contact-us/find-a-branch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical activity plays an important role in your health, well-being and quality of life. Get tips and tools to improve and maintain your health: 
-       - [Practical tips for seniors (65 years and older)](https://www.canada.ca/en/public-health/services/publications/healthy-living/physical-activity-tips-older-adults-65-years-older.html)
-       - [Canadian 24-hour movement guidelines](https://www.participaction.com/the-science/benefits-and-guidelines/adults-65-plus/)
-       - [Physical Activity Toolkit: For Older Adults (site en anglais seulement)](https://prismic-io.s3.amazonaws.com/participaction/84f1e964-a43c-419e-994b-57a63c3bf822_pa-seniors-toolkit-design-v03-eng-pa.pdf)
-       -  [Aging: Move Now, for a Healthy Future](https://www.participaction.com/the-science/explore-benefits/aging/)
-       -  [McMaster Optimal Aging Portal: Information on Healthy Aging](https://www.mcmasteroptimalaging.org/)
-       - [Canada's Food Guide: Healthy Eating for Seniors](https://food-guide.canada.ca/en/tips-for-healthy-eating/seniors/)
-       - [Physical Activity Promotion and Falls Prevention Initiative](https://www.ontario.ca/page/exercise-and-falls-prevention-programs)
-       - [Brain-friendly tips to reduce your risk of dementia](https://alzheimer.ca/en/about-dementia/how-can-i-reduce-risk-dementia/brain-healthy-tips-reduce-your-risk-dementia)
-       - [All about sleep: everything you need to better understand sleep and its importance to your health](https://sleeponitcanada.ca/all-about-sleep/)
-       - [A social adventure is good!](https://www.activeagingcanada.ca/blog/)
-       - [Separated, but not alone: the importance of social ties in old age](https://kmb.camh.ca/eenet/resources/connection-matters-in-later-life)
-       - [A friendly voice](https://afriendlyvoice.ca/) allows seniors to chat with a friendly and well-being person, without waiting or judgment
-Find exercise and activity programs near you: 
-       - [211Ontario](https://211ontario.ca/search/)
-       - Active Living Centre Programs for Seniors  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Make choices while you are competent about how you wish to be cared for in the future (if you become incapable):  
-  - read [what every older Canadian should know about planning for possible loss of independence](https://www.canada.ca/en/employment-social-development/corporate/seniors/forum/independence-loss-planning.html)  
-  - find helpful tools, at [Advance Care Planning Ontario,](https://www.advancecareplanningontario.ca/)  and learn about the process of advance care planning 
-  - contact a [local Alzheimer’s Society chapter](https://alzheimer.ca/en/help-support/find-your-areas-alzheimer-society) to see if they offer advance care planning seminars in your community 
-  - print and fill-out [your substitute decision-maker wallet card](https://files.ontario.ca/advancedcare.walletcard.pdf) with important information in the event of an emergency </t>
-  </si>
-  <si>
-    <t>Before, during or after you make a purchase, learn your rights and find the information you need to know to protect yourself, including: 
-   - [identifying a scam or fraud](https://www.ontario.ca/page/identify-scam-or-fraud)
-   - [door-to-door sales and home service contracts](https://www.ontario.ca/page/door-door-sales-and-home-service-contracts)
-   - [planning funerals and arrangement](https://www.ontario.ca/page/consumer-protection-when-planning-funeral-burial-cremation-or-scattering)</t>
-  </si>
-  <si>
     <t>Get help paying for prescription drugs.  
 It also helps you pay for some: 
   - [allergy shots and epinephrine injectable products](https://www.ontario.ca/page/get-coverage-prescription-drugs#allergy) 
@@ -2350,13 +2310,6 @@
   - [support and treatments to quit smoking](https://www.ontario.ca/page/get-coverage-prescription-drugs#section-2)</t>
   </si>
   <si>
-    <t>Learn how and when to get vaccinated, a flu shot or immunized to protect yourself and others against preventable diseases and serious illness. 
-   - [Flu shots](https://www.ontario.ca/page/flu-facts)
-   - [Vaccines for adults](https://www.ontario.ca/page/vaccines-adults#section-1)
-   - [COVID-19 vaccines](https://www.ontario.ca/page/covid-19-vaccines)
-   - [Ontario's Routine Immunization Schedule](https://www.health.gov.on.ca/en/public/programs/immunization/static/immunization_tool.html)</t>
-  </si>
-  <si>
     <t>Join free classes to help maintain balance, strength and prevent falls.  
 Resources to help reduce your risk: 
   - [Too Fit To Fracture: exercise recommendations](https://osteoporosis.ca/exercise-recommendations/)
@@ -2366,12 +2319,59 @@
   - [Steps to Stair Safety at Home](https://www.canada.ca/en/public-health/services/health-promotion/aging-seniors/publications/publications-general-public/stair-safety.html)</t>
   </si>
   <si>
+    <t>Future Care</t>
+  </si>
+  <si>
+    <t>Physical activity plays an important role in your health, well-being and quality of life. Get tips and tools to improve and maintain your health: 
+  - [Practical tips for seniors (65 years and older)](https://www.canada.ca/en/public-health/services/publications/healthy-living/physical-activity-tips-older-adults-65-years-older.html)
+  - [Canadian 24-hour movement guidelines](https://www.participaction.com/the-science/benefits-and-guidelines/adults-65-plus/)
+  - [Physical Activity Toolkit: For Older Adults (site en anglais seulement)](https://prismic-io.s3.amazonaws.com/participaction/84f1e964-a43c-419e-994b-57a63c3bf822_pa-seniors-toolkit-design-v03-eng-pa.pdf)
+  - [Aging: Move Now, for a Healthy Future](https://www.participaction.com/the-science/explore-benefits/aging/)
+  - [McMaster Optimal Aging Portal: Information on Healthy Aging](https://www.mcmasteroptimalaging.org/)
+  - [Canada's Food Guide: Healthy Eating for Seniors](https://food-guide.canada.ca/en/tips-for-healthy-eating/seniors/)
+  - [Physical Activity Promotion and Falls Prevention Initiative](https://www.ontario.ca/page/exercise-and-falls-prevention-programs)
+  - [Brain-friendly tips to reduce your risk of dementia](https://alzheimer.ca/en/about-dementia/how-can-i-reduce-risk-dementia/brain-healthy-tips-reduce-your-risk-dementia)
+  - [All about sleep: everything you need to better understand sleep and its importance to your health](https://sleeponitcanada.ca/all-about-sleep/)
+  - [A social adventure is good!](https://www.activeagingcanada.ca/blog/)
+  - [Separated, but not alone: the importance of social ties in old age](https://kmb.camh.ca/eenet/resources/connection-matters-in-later-life)
+  - [A friendly voice](https://afriendlyvoice.ca/) allows seniors to chat with a friendly and well-being person, without waiting or judgment
+Find exercise and activity programs near you: 
+  - [211Ontario](https://211ontario.ca/search/)
+  - Active Living Centre Programs for Seniors</t>
+  </si>
+  <si>
     <t>Find out what services OHIP covers when you leave Canada temporarily. 
-    -  [Out-of-province or out-of-country treatment claim form](https://forms.mgcs.gov.on.ca/en/dataset/014-0951-84)
-    -  [How to get reimbursed for supported prescription drugs](https://www.ontario.ca/page/get-coverage-prescription-drugs)</t>
-  </si>
-  <si>
-    <t>Future Care</t>
+  - [Out-of-province or out-of-country treatment claim form](https://forms.mgcs.gov.on.ca/en/dataset/014-0951-84)
+  - [How to get reimbursed for supported prescription drugs](https://www.ontario.ca/page/get-coverage-prescription-drugs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make choices while you are competent about how you wish to be cared for in the future (if you become incapable):  
+  - read [what every older Canadian should know about planning for possible loss of independence](https://www.canada.ca/en/employment-social-development/corporate/seniors/forum/independence-loss-planning.html)  
+  - find helpful tools, at [Advance Care Planning Ontario,](https://www.advancecareplanningontario.ca/)  and learn about the process of advance care planning 
+  - contact a [local Alzheimer’s Society chapter](https://alzheimer.ca/en/help-support/find-your-areas-alzheimer-society) to see if they offer advance care planning seminars in your community 
+  - print and fill-out [your substitute decision-maker wallet card](https://files.ontario.ca/advancedcare.walletcard.pdf) with important information in the event of an emergency </t>
+  </si>
+  <si>
+    <t>Before, during or after you make a purchase, learn your rights and find the information you need to know to protect yourself, including: 
+  - [identifying a scam or fraud](https://www.ontario.ca/page/identify-scam-or-fraud)
+  - [door-to-door sales and home service contracts](https://www.ontario.ca/page/door-door-sales-and-home-service-contracts)
+  - [planning funerals and arrangement](https://www.ontario.ca/page/consumer-protection-when-planning-funeral-burial-cremation-or-scattering)</t>
+  </si>
+  <si>
+    <t>Learn how and when to get vaccinated, a flu shot or immunized to protect yourself and others against preventable diseases and serious illness. 
+  - [Flu shots](https://www.ontario.ca/page/flu-facts)
+  - [Vaccines for adults](https://www.ontario.ca/page/vaccines-adults#section-1)
+  - [COVID-19 vaccines](https://www.ontario.ca/page/covid-19-vaccines)
+  - [Ontario's Routine Immunization Schedule](https://www.health.gov.on.ca/en/public/programs/immunization/static/immunization_tool.html)</t>
+  </si>
+  <si>
+    <t>Use our map to find programs that promote wellness, social connectedness and learning in your community.
+Clubs and groups
+Find social activities and hobbies in your community through organizations such as: 
+  - [YMCA](https://www.ymca.ca/locations?type=ymca,camps&amp;amenities)
+  - [Club Rotary](https://my.rotary.org/en/club-search)
+  - [Lions Club](https://www.lionsclubs.org/en/start-our-approach/club-locator)
+  - [Royal Canadian Legion](https://legion.ca/contact-us/find-a-branch)</t>
   </si>
 </sst>
 </file>
@@ -4595,7 +4595,7 @@
         <v>255</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>256</v>
@@ -5115,7 +5115,7 @@
         <v>327</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>328</v>
@@ -5175,7 +5175,7 @@
         <v>337</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>338</v>
@@ -5755,7 +5755,7 @@
         <v>425</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>426</v>
@@ -6035,9 +6035,12 @@
         <v>653</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C161" s="7"/>
+      <c r="D161" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E161" s="5" t="s">
         <v>427</v>
       </c>
@@ -6170,7 +6173,7 @@
         <v>487</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>488</v>
@@ -6725,12 +6728,12 @@
         <v>548</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="270">
+    <row r="196" spans="1:6" ht="225">
       <c r="A196" s="13" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C196" s="7"/>
       <c r="E196" s="5" t="s">
@@ -6760,12 +6763,12 @@
         <v>573</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="150">
+    <row r="198" spans="1:6" ht="120">
       <c r="A198" s="13" t="s">
         <v>577</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>578</v>
@@ -7417,15 +7420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Contains xmlns="9f0160d9-aef1-48fe-ba90-8497f3ce61fd" xsi:nil="true"/>
@@ -7435,6 +7429,15 @@
     <TaxCatchAll xmlns="b43189f3-2cc4-40ec-a659-b64b0f160aa1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7677,20 +7680,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E33242-4F2B-43E4-9B51-E63A092159C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C882F68F-59D5-432B-84FD-AE141FC9A57B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9f0160d9-aef1-48fe-ba90-8497f3ce61fd"/>
     <ds:schemaRef ds:uri="b43189f3-2cc4-40ec-a659-b64b0f160aa1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E33242-4F2B-43E4-9B51-E63A092159C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
